--- a/data/trans_orig/IMC_inf_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25543</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40505</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>30388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>39571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>33310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55169</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70131</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36957</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51700</t>
+          <t>51612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61988</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82316</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56097</t>
+          <t>56117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>85682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106209</t>
+          <t>106802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>31114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>46706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>39561</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49042</t>
+          <t>49010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32070</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73620</t>
+          <t>73027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90525</t>
+          <t>90053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>33373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>46827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45459</t>
+          <t>46004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75446</t>
+          <t>74805</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>93614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23891</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28860</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50905</t>
+          <t>50794</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22706</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>25775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>33350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>48015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42575</t>
+          <t>42551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57374</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73529</t>
+          <t>73187</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>37522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55173</t>
+          <t>55639</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70226</t>
+          <t>70071</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92929</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71262</t>
+          <t>72663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88336</t>
+          <t>88863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>79357</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139581</t>
+          <t>138137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>162284</t>
+          <t>162439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68313</t>
+          <t>67168</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48958</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65253</t>
+          <t>65750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102860</t>
+          <t>102633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>128228</t>
+          <t>128151</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59048</t>
+          <t>60193</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>77850</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>51748</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68540</t>
+          <t>69130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116630</t>
+          <t>116707</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>141998</t>
+          <t>142225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>187155</t>
+          <t>186354</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>221822</t>
+          <t>221172</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>255946</t>
+          <t>253811</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>293625</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>452143</t>
+          <t>450305</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>506013</t>
+          <t>505438</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>356250</t>
+          <t>356900</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>390917</t>
+          <t>391718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>309957</t>
+          <t>311828</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>351642</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>677512</t>
+          <t>678087</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>731382</t>
+          <t>733220</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23756</t>
+          <t>24020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>37476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>51684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36027</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30769</t>
+          <t>31205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45415</t>
+          <t>45950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56899</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76967</t>
+          <t>76032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,51%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37860</t>
+          <t>37564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50982</t>
+          <t>51319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34260</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>48470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76595</t>
+          <t>77530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96663</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36294</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>24504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69597</t>
+          <t>69054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,42%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>22813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>49155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>66858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35828</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37113</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54921</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31514</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42993</t>
+          <t>42789</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>20057</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>55268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72476</t>
+          <t>72847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28910</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27111</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46725</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31118</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36564</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>48798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65422</t>
+          <t>65207</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52851</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55471</t>
+          <t>54189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72503</t>
+          <t>72521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94874</t>
+          <t>95467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121773</t>
+          <t>121168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58586</t>
+          <t>58408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75510</t>
+          <t>75462</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43841</t>
+          <t>43823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60873</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>106008</t>
+          <t>106613</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132907</t>
+          <t>132314</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51897</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69707</t>
+          <t>70313</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59767</t>
+          <t>60467</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78458</t>
+          <t>78112</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117077</t>
+          <t>116156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>141561</t>
+          <t>142206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51985</t>
+          <t>51379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69795</t>
+          <t>70363</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>46942</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65287</t>
+          <t>64587</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105184</t>
+          <t>104539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129668</t>
+          <t>130589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>201556</t>
+          <t>204318</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239622</t>
+          <t>242337</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>260698</t>
+          <t>262113</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>298687</t>
+          <t>300282</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>475219</t>
+          <t>474635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>527639</t>
+          <t>526569</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>284693</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>325474</t>
+          <t>322712</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>257924</t>
+          <t>256329</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>295913</t>
+          <t>294498</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>556002</t>
+          <t>557072</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>608422</t>
+          <t>609006</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21082</t>
+          <t>20755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>28296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>41959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44295</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42787</t>
+          <t>42559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41949</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57241</t>
+          <t>57240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72899</t>
+          <t>73760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95172</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41695</t>
+          <t>41923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56647</t>
+          <t>56914</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32965</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48257</t>
+          <t>48279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79516</t>
+          <t>79706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101789</t>
+          <t>100928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>48232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>45833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44184</t>
+          <t>45032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70079</t>
+          <t>70210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87240</t>
+          <t>87647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>34346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>38874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57285</t>
+          <t>56515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38097</t>
+          <t>38380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52904</t>
+          <t>53674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71008</t>
+          <t>71315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>41486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>54331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48009</t>
+          <t>48370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27345</t>
+          <t>27340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>37949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31086</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49518</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66400</t>
+          <t>65226</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>24215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31591</t>
+          <t>31653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>47555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59104</t>
+          <t>60013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82089</t>
+          <t>82330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>66448</t>
+          <t>66414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>81485</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66858</t>
+          <t>66706</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82670</t>
+          <t>82608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>137448</t>
+          <t>137207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>160433</t>
+          <t>159524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>37281</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>54134</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54810</t>
+          <t>54977</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73627</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96925</t>
+          <t>96554</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121857</t>
+          <t>122866</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71907</t>
+          <t>70909</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87939</t>
+          <t>87762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63647</t>
+          <t>64534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82464</t>
+          <t>82297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140459</t>
+          <t>139450</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>165391</t>
+          <t>165762</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170642</t>
+          <t>170586</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208172</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>241033</t>
+          <t>241538</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>280406</t>
+          <t>281183</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>425364</t>
+          <t>422726</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>481685</t>
+          <t>477154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>336230</t>
+          <t>336319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>373760</t>
+          <t>373816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>303528</t>
+          <t>302751</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>342396</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>646651</t>
+          <t>651182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>702972</t>
+          <t>705610</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>40607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34840</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39212</t>
+          <t>39395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51507</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77963</t>
+          <t>76779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96522</t>
+          <t>96039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45969</t>
+          <t>45280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39811</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63876</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50111</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>102394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72970</t>
+          <t>73659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104403</t>
+          <t>103566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>48425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73288</t>
+          <t>73649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130567</t>
+          <t>129644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181927</t>
+          <t>175942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22446</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34669</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50561</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,95%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40603</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>33719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56300</t>
+          <t>55625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>71601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>19273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>29221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19635</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39406</t>
+          <t>39596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54612</t>
+          <t>52971</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67058</t>
+          <t>64827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89888</t>
+          <t>88244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>25593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>15877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36578</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49442</t>
+          <t>49510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>34535</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25695</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33947</t>
+          <t>33712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53798</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67181</t>
+          <t>67015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45531</t>
+          <t>45356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>44444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68049</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79049</t>
+          <t>77762</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106733</t>
+          <t>106198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>61989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79454</t>
+          <t>79882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66161</t>
+          <t>65609</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>90117</t>
+          <t>89766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>135357</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>162506</t>
+          <t>163793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39612</t>
+          <t>39370</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41595</t>
+          <t>40511</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60549</t>
+          <t>60683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69050</t>
+          <t>67882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94689</t>
+          <t>94355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81383</t>
+          <t>81625</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97472</t>
+          <t>97524</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78495</t>
+          <t>78361</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>97449</t>
+          <t>98533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>165350</t>
+          <t>165684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>190989</t>
+          <t>192157</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138492</t>
+          <t>136345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>185800</t>
+          <t>185752</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>229878</t>
+          <t>228801</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>282178</t>
+          <t>279715</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380194</t>
+          <t>379725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>453554</t>
+          <t>453220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>389570</t>
+          <t>389618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>436878</t>
+          <t>439025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>370674</t>
+          <t>373137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>422974</t>
+          <t>424051</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>774668</t>
+          <t>775002</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>848028</t>
+          <t>848497</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
